--- a/output/pdf_financials_xlsx/MDA.xlsx
+++ b/output/pdf_financials_xlsx/MDA.xlsx
@@ -1255,22 +1255,22 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>39.3</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>22.5</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>166.7</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>152</v>
       </c>
     </row>
     <row r="35">
@@ -1305,22 +1305,22 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>39.3</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>22.5</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>166.7</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>152</v>
       </c>
     </row>
     <row r="37">
@@ -3938,7 +3938,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">

--- a/output/pdf_financials_xlsx/MDA.xlsx
+++ b/output/pdf_financials_xlsx/MDA.xlsx
@@ -1123,22 +1123,22 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>46.1</v>
+        <v>42.2</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>61</v>
+        <v>56.3</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>58.2</v>
+        <v>52.5</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>55.4</v>
+        <v>46.5</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>59.3</v>
+        <v>47</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>98.3</v>
+        <v>84.59999999999999</v>
       </c>
     </row>
     <row r="29">
@@ -1148,22 +1148,22 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>28.3</v>
+        <v>24.4</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>72.3</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>92</v>
+        <v>86.3</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>120.7</v>
+        <v>111.8</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>163.3</v>
+        <v>151</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>242.9</v>
+        <v>229.2</v>
       </c>
     </row>
     <row r="30">
@@ -1173,22 +1173,22 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>9.573748308525033</v>
+        <v>8.254397834912043</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>15.16041098762843</v>
+        <v>14.17487942964982</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>14.34809731752963</v>
+        <v>13.45913911416095</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>14.94551758296186</v>
+        <v>13.84348687469044</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>15.11897046569762</v>
+        <v>13.9801870197204</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>14.87264266470732</v>
+        <v>14.03379867744306</v>
       </c>
     </row>
     <row r="31">
@@ -2899,22 +2899,22 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>0</v>
+        <v>58.3</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>79.8</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>76.2</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>140.6</v>
       </c>
     </row>
     <row r="101">
@@ -11224,7 +11224,11 @@
           <t>Depreciation of property, plant, and equipment 14</t>
         </is>
       </c>
-      <c r="D165" t="inlineStr"/>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E165" t="inlineStr">
         <is>
           <t>-</t>
@@ -11268,7 +11272,11 @@
           <t>Depreciation of right-of-use assets 15</t>
         </is>
       </c>
-      <c r="D166" t="inlineStr"/>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E166" t="inlineStr">
         <is>
           <t>-</t>
@@ -11314,7 +11322,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -12762,7 +12770,11 @@
           <t>Depreciation of property, plant, and equipment 13</t>
         </is>
       </c>
-      <c r="D200" t="inlineStr"/>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E200" t="inlineStr">
         <is>
           <t>-</t>
@@ -12806,7 +12818,11 @@
           <t>Depreciation of right-of-use assets 14</t>
         </is>
       </c>
-      <c r="D201" t="inlineStr"/>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E201" t="inlineStr">
         <is>
           <t>-</t>
@@ -12852,7 +12868,7 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
@@ -13648,7 +13664,11 @@
           <t>Depreciation of property, plant, and equipment 12</t>
         </is>
       </c>
-      <c r="D220" t="inlineStr"/>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E220" t="inlineStr">
         <is>
           <t>-</t>
@@ -13692,7 +13712,11 @@
           <t>Depreciation of right-of-use assets 13</t>
         </is>
       </c>
-      <c r="D221" t="inlineStr"/>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E221" t="inlineStr">
         <is>
           <t>-</t>
@@ -13738,7 +13762,7 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
@@ -14282,7 +14306,11 @@
           <t>Depreciation of property, plant and equipment 11</t>
         </is>
       </c>
-      <c r="D234" t="inlineStr"/>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E234" s="5" t="n">
         <v>5.3</v>
       </c>
@@ -14324,7 +14352,11 @@
           <t>Depreciation of right-of-use assets 12</t>
         </is>
       </c>
-      <c r="D235" t="inlineStr"/>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E235" s="5" t="n">
         <v>6.9</v>
       </c>
@@ -14368,7 +14400,7 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E236" s="5" t="n">
@@ -16478,7 +16510,7 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
@@ -16502,10 +16534,10 @@
         </is>
       </c>
       <c r="I283" s="5" t="n">
-        <v>-47</v>
+        <v>47</v>
       </c>
       <c r="J283" s="5" t="n">
-        <v>-84.59999999999999</v>
+        <v>84.59999999999999</v>
       </c>
     </row>
     <row r="284">
@@ -17690,7 +17722,7 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
@@ -17709,10 +17741,10 @@
         </is>
       </c>
       <c r="H310" s="5" t="n">
-        <v>-46.5</v>
+        <v>46.5</v>
       </c>
       <c r="I310" s="5" t="n">
-        <v>-47</v>
+        <v>47</v>
       </c>
       <c r="J310" t="inlineStr">
         <is>
@@ -18888,7 +18920,7 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
@@ -18902,10 +18934,10 @@
         </is>
       </c>
       <c r="G337" s="5" t="n">
-        <v>-52.5</v>
+        <v>52.5</v>
       </c>
       <c r="H337" s="5" t="n">
-        <v>-46.5</v>
+        <v>46.5</v>
       </c>
       <c r="I337" t="inlineStr">
         <is>
@@ -19560,17 +19592,17 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E352" s="5" t="n">
-        <v>-42.2</v>
+        <v>42.2</v>
       </c>
       <c r="F352" s="5" t="n">
-        <v>-56.3</v>
+        <v>56.3</v>
       </c>
       <c r="G352" s="5" t="n">
-        <v>-52.5</v>
+        <v>52.5</v>
       </c>
       <c r="H352" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/MDA.xlsx
+++ b/output/pdf_financials_xlsx/MDA.xlsx
@@ -824,7 +824,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0.5</v>
+        <v>-0.5</v>
       </c>
       <c r="C17" s="3" t="n">
         <v>8.4</v>
@@ -3074,16 +3074,16 @@
         </is>
       </c>
       <c r="B107" s="3" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="C107" s="3" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="D107" s="3" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="E107" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F107" s="3" t="n">
         <v>0</v>
@@ -3650,10 +3650,8 @@
       <c r="F129" s="3" t="n">
         <v>-436.1</v>
       </c>
-      <c r="G129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G129" s="3" t="n">
+        <v>196.3</v>
       </c>
     </row>
     <row r="130">
@@ -3800,12 +3798,10 @@
         <v>-134.5</v>
       </c>
       <c r="F135" s="3" t="n">
-        <v>819.7</v>
-      </c>
-      <c r="G135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>805.7</v>
+      </c>
+      <c r="G135" s="3" t="n">
+        <v>374.3</v>
       </c>
     </row>
   </sheetData>
@@ -11806,7 +11802,11 @@
           <t>Net cash generated in operating activities</t>
         </is>
       </c>
-      <c r="D178" t="inlineStr"/>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E178" t="inlineStr">
         <is>
           <t>-</t>
@@ -13808,7 +13808,11 @@
           <t>Share-based compensation expense 19</t>
         </is>
       </c>
-      <c r="D223" t="inlineStr"/>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E223" t="inlineStr">
         <is>
           <t>-</t>
@@ -14444,7 +14448,11 @@
           <t>Share-based compensation expense 18</t>
         </is>
       </c>
-      <c r="D237" t="inlineStr"/>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E237" s="5" t="n">
         <v>4.9</v>
       </c>
@@ -20944,7 +20952,11 @@
           <t>Income tax recovery (expense) 22</t>
         </is>
       </c>
-      <c r="D382" t="inlineStr"/>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E382" s="5" t="n">
         <v>0.5</v>
       </c>
